--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -1244,27 +1244,27 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2419350" cy="2419350"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="0" name="image1.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
+<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2419350" cy="2419350"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:prstGeom prst="rect">
           <avLst/>
         </a:prstGeom>
@@ -1272,35 +1272,35 @@
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2419350" cy="2419350"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="0" name="image1.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
+<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2419350" cy="2419350"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:prstGeom prst="rect">
           <avLst/>
         </a:prstGeom>
@@ -1308,11 +1308,11 @@
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7406,6 +7406,7 @@
     <col width="51.13" customWidth="1" style="204" min="4" max="4"/>
     <col width="48.38" customWidth="1" style="204" min="5" max="8"/>
     <col width="23.63" customWidth="1" style="204" min="9" max="9"/>
+    <col width="48.38" customWidth="1" style="204" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7550,6 +7551,12 @@
 </t>
         </is>
       </c>
+      <c r="J11" s="203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comments/Remarks
+Add any notes or details about this agency.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30.75" customHeight="1" s="204">
       <c r="B12" s="73" t="n"/>
@@ -7648,9 +7655,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8394,6 +8401,7 @@
     <col width="35" customWidth="1" style="204" min="8" max="8"/>
     <col width="48.38" customWidth="1" style="204" min="9" max="9"/>
     <col width="23.63" customWidth="1" style="204" min="10" max="13"/>
+    <col width="48.38" customWidth="1" style="204" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8677,6 +8685,12 @@
 </t>
         </is>
       </c>
+      <c r="N17" s="203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assigned Recruiters
+Recruiters assigned to this campaign. Separate multiple names with commas.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30.75" customHeight="1" s="204">
       <c r="B18" s="50" t="inlineStr">
@@ -8744,10 +8758,10 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B6:M6"/>
-    <mergeCell ref="B15:M15"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B5:M5"/>
+    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="B15:N15"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="B5:N5"/>
     <mergeCell ref="J16:M16"/>
   </mergeCells>
   <hyperlinks>
@@ -8774,6 +8788,7 @@
     <col width="12.75" customWidth="1" style="204" min="2" max="2"/>
     <col width="32" customWidth="1" style="204" min="3" max="9"/>
     <col width="23.63" customWidth="1" style="204" min="10" max="10"/>
+    <col width="48.38" customWidth="1" style="204" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8928,6 +8943,12 @@
 </t>
         </is>
       </c>
+      <c r="K11" s="203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comments/Remarks
+Add any notes or details about this site.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30.75" customHeight="1" s="204">
       <c r="B12" s="50" t="inlineStr">
@@ -8985,9 +9006,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B9:J9"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B9:K9"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B5:K5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="F12:F13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -9018,6 +9039,7 @@
     <col width="16.13" customWidth="1" style="204" min="7" max="7"/>
     <col width="48.38" customWidth="1" style="204" min="8" max="11"/>
     <col width="23.63" customWidth="1" style="204" min="12" max="12"/>
+    <col width="23.63" customWidth="1" style="204" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9297,6 +9319,12 @@
 </t>
         </is>
       </c>
+      <c r="M17" s="203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Category
+Whether this is a Pre-screening or a Follow-up question.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30.75" customHeight="1" s="204">
       <c r="A18" s="89" t="n"/>
@@ -9683,10 +9711,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="B5:M5"/>
     <mergeCell ref="K16:L16"/>
-    <mergeCell ref="B14:L14"/>
-    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B14:M14"/>
+    <mergeCell ref="B3:M3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D18:D27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
